--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.06611570247933884</v>
+        <v>0.05185185185185185</v>
       </c>
       <c r="B2">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1901408450704225</v>
+        <v>0.07746478873239436</v>
       </c>
       <c r="D2">
-        <v>0.9274193548387096</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="E2">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.05185185185185185</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -429,16 +429,16 @@
         <v>0.07746478873239436</v>
       </c>
       <c r="D2">
-        <v>0.9492753623188406</v>
+        <v>0.9424460431654677</v>
       </c>
       <c r="E2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
